--- a/cox1 homologs/Homologs annotations and stats.xlsx
+++ b/cox1 homologs/Homologs annotations and stats.xlsx
@@ -1,12 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aditya/Desktop/gen_bio_cw/cox1 homologs/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{691DF3F1-2A9D-D74B-921C-772FEE04BEBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -36,10 +45,10 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Lexend"/>
-        <color rgb="FF1155CC"/>
-        <sz val="10.0"/>
-        <u/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Lexend"/>
       </rPr>
       <t>P00397.2</t>
     </r>
@@ -56,10 +65,10 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Lexend"/>
-        <color rgb="FF1155CC"/>
-        <sz val="10.0"/>
-        <u/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Lexend"/>
       </rPr>
       <t>P00395.1</t>
     </r>
@@ -70,10 +79,10 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Lexend"/>
-        <color rgb="FF1155CC"/>
-        <sz val="10.0"/>
-        <u/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Lexend"/>
       </rPr>
       <t>P00399.2</t>
     </r>
@@ -84,10 +93,10 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Lexend"/>
-        <color rgb="FF1155CC"/>
-        <sz val="10.0"/>
-        <u/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Lexend"/>
       </rPr>
       <t>AWM96690.1</t>
     </r>
@@ -104,10 +113,10 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Lexend"/>
-        <color rgb="FF1155CC"/>
-        <sz val="10.0"/>
-        <u/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Lexend"/>
       </rPr>
       <t>P00401.2</t>
     </r>
@@ -118,10 +127,10 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Lexend"/>
-        <color rgb="FF1155CC"/>
-        <sz val="10.0"/>
-        <u/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Lexend"/>
       </rPr>
       <t>P07657.4</t>
     </r>
@@ -132,10 +141,10 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Lexend"/>
-        <color rgb="FF1155CC"/>
-        <sz val="10.0"/>
-        <u/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Lexend"/>
       </rPr>
       <t>YP_316586.1</t>
     </r>
@@ -146,10 +155,10 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Lexend"/>
-        <color rgb="FF1155CC"/>
-        <sz val="10.0"/>
-        <u/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Lexend"/>
       </rPr>
       <t>P60620.1</t>
     </r>
@@ -160,17 +169,17 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Lexend"/>
-        <color rgb="FF1155CC"/>
-        <sz val="10.0"/>
-        <u/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Lexend"/>
       </rPr>
       <t>WP_310900782.</t>
     </r>
     <r>
       <rPr>
-        <rFont val="Lexend"/>
-        <sz val="10.0"/>
+        <sz val="10"/>
+        <rFont val="Lexend"/>
       </rPr>
       <t>1</t>
     </r>
@@ -181,10 +190,10 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Lexend"/>
-        <color rgb="FF1155CC"/>
-        <sz val="10.0"/>
-        <u/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Lexend"/>
       </rPr>
       <t>WP_012214567.1</t>
     </r>
@@ -195,10 +204,10 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Lexend"/>
-        <color rgb="FF1155CC"/>
-        <sz val="10.0"/>
-        <u/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Lexend"/>
       </rPr>
       <t>OLS27277.1</t>
     </r>
@@ -209,10 +218,10 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Lexend"/>
-        <color rgb="FF1155CC"/>
-        <sz val="10.0"/>
-        <u/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Lexend"/>
       </rPr>
       <t>RCJ35289.1</t>
     </r>
@@ -223,10 +232,10 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Lexend"/>
-        <color rgb="FF1155CC"/>
-        <sz val="10.0"/>
-        <u/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Lexend"/>
       </rPr>
       <t>P24010.3</t>
     </r>
@@ -237,17 +246,17 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Lexend"/>
-        <color rgb="FF1155CC"/>
-        <sz val="10.0"/>
-        <u/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Lexend"/>
       </rPr>
       <t>Q9K451.</t>
     </r>
     <r>
       <rPr>
-        <rFont val="Lexend"/>
-        <sz val="10.0"/>
+        <sz val="10"/>
+        <rFont val="Lexend"/>
       </rPr>
       <t>1</t>
     </r>
@@ -261,10 +270,10 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Lexend"/>
-        <color rgb="FF1155CC"/>
-        <sz val="10.0"/>
-        <u/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Lexend"/>
       </rPr>
       <t>HCH0557098.1</t>
     </r>
@@ -275,10 +284,10 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Lexend"/>
-        <color rgb="FF1155CC"/>
-        <sz val="10.0"/>
-        <u/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Lexend"/>
       </rPr>
       <t>BFO88488.1</t>
     </r>
@@ -289,10 +298,10 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Lexend"/>
-        <color rgb="FF1155CC"/>
-        <sz val="10.0"/>
-        <u/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Lexend"/>
       </rPr>
       <t>AAF78815.1</t>
     </r>
@@ -304,147 +313,134 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="11">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Lexend"/>
     </font>
     <font>
       <i/>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Lexend"/>
     </font>
     <font>
       <u/>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Lexend"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Lexend"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF212121"/>
       <name val="Lexend"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Lexend"/>
     </font>
     <font>
       <u/>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Lexend"/>
     </font>
     <font>
       <i/>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF131312"/>
       <name val="Lexend"/>
     </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF1155CC"/>
+      <name val="Lexend"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Lexend"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD5DEE3"/>
-        <bgColor rgb="FFD5DEE3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="14">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="11" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="5" numFmtId="10" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="9" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="5" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="5" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -634,22 +630,25 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:G19"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="25.13"/>
-    <col customWidth="1" min="2" max="2" width="17.88"/>
-    <col customWidth="1" min="5" max="5" width="16.0"/>
+    <col min="1" max="1" width="25.1640625" customWidth="1"/>
+    <col min="2" max="2" width="17.83203125" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:7" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -668,375 +667,394 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="G1" s="2"/>
+    </row>
+    <row r="2" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="D2" s="5">
-        <v>0.9102</v>
-      </c>
-      <c r="E2" s="4" t="s">
+      <c r="C2" s="5">
+        <v>0</v>
+      </c>
+      <c r="D2" s="6">
+        <v>0.91020000000000001</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="s">
+      <c r="F2" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="2"/>
+    </row>
+    <row r="3" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="D3" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="E3" s="4" t="s">
+      <c r="C3" s="5">
+        <v>0</v>
+      </c>
+      <c r="D3" s="8">
+        <v>1</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
+      <c r="F3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="2"/>
+    </row>
+    <row r="4" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="D4" s="5">
-        <v>0.7624</v>
-      </c>
-      <c r="E4" s="4" t="s">
+      <c r="C4" s="5">
+        <v>0</v>
+      </c>
+      <c r="D4" s="6">
+        <v>0.76239999999999997</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="s">
+      <c r="F4" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" s="2"/>
+    </row>
+    <row r="5" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="9">
-        <v>2.0E-99</v>
-      </c>
-      <c r="D5" s="4">
+      <c r="C5" s="10">
+        <v>2E-99</v>
+      </c>
+      <c r="D5" s="5">
         <v>74.89</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="5" t="s">
         <v>16</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="10" t="s">
+      <c r="G5" s="2"/>
+    </row>
+    <row r="6" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A6" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="D6" s="5">
-        <v>0.569</v>
-      </c>
-      <c r="E6" s="11" t="s">
+      <c r="C6" s="5">
+        <v>0</v>
+      </c>
+      <c r="D6" s="6">
+        <v>0.56899999999999995</v>
+      </c>
+      <c r="E6" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="10" t="s">
+      <c r="F6" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6" s="2"/>
+    </row>
+    <row r="7" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A7" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="D7" s="5">
-        <v>0.557</v>
-      </c>
-      <c r="E7" s="4" t="s">
+      <c r="C7" s="5">
+        <v>0</v>
+      </c>
+      <c r="D7" s="6">
+        <v>0.55700000000000005</v>
+      </c>
+      <c r="E7" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F7" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="10" t="s">
+      <c r="F7" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G7" s="2"/>
+    </row>
+    <row r="8" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A8" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="D8" s="5">
-        <v>0.7069</v>
-      </c>
-      <c r="E8" s="4" t="s">
+      <c r="C8" s="5">
+        <v>0</v>
+      </c>
+      <c r="D8" s="6">
+        <v>0.70689999999999997</v>
+      </c>
+      <c r="E8" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F8" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="10" t="s">
+      <c r="F8" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G8" s="2"/>
+    </row>
+    <row r="9" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A9" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C9" s="5">
+        <v>0</v>
+      </c>
+      <c r="D9" s="6">
         <v>0.6986</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="s">
+      <c r="F9" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G9" s="2"/>
+    </row>
+    <row r="10" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A10" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="9">
-        <v>2.0E-134</v>
-      </c>
-      <c r="D10" s="5">
-        <v>0.4384</v>
-      </c>
-      <c r="E10" s="4" t="s">
+      <c r="C10" s="10">
+        <v>2.0000000000000001E-134</v>
+      </c>
+      <c r="D10" s="6">
+        <v>0.43840000000000001</v>
+      </c>
+      <c r="E10" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="10" t="s">
+      <c r="F10" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G10" s="2"/>
+    </row>
+    <row r="11" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A11" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="9">
-        <v>2.0E-103</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C11" s="10">
+        <v>1.9999999999999999E-103</v>
+      </c>
+      <c r="D11" s="6">
         <v>0.3901</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="10" t="s">
+      <c r="F11" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G11" s="2"/>
+    </row>
+    <row r="12" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A12" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C12" s="9">
-        <v>4.0E-98</v>
-      </c>
-      <c r="D12" s="5">
-        <v>0.384</v>
-      </c>
-      <c r="E12" s="4" t="s">
+      <c r="C12" s="10">
+        <v>3.9999999999999998E-98</v>
+      </c>
+      <c r="D12" s="6">
+        <v>0.38400000000000001</v>
+      </c>
+      <c r="E12" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F12" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="10" t="s">
+      <c r="F12" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G12" s="2"/>
+    </row>
+    <row r="13" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A13" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="C13" s="9">
-        <v>2.0E-142</v>
-      </c>
-      <c r="D13" s="5">
-        <v>0.4438</v>
-      </c>
-      <c r="E13" s="4" t="s">
+      <c r="C13" s="10">
+        <v>2.0000000000000001E-142</v>
+      </c>
+      <c r="D13" s="6">
+        <v>0.44379999999999997</v>
+      </c>
+      <c r="E13" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F13" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="10" t="s">
+      <c r="F13" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G13" s="2"/>
+    </row>
+    <row r="14" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A14" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="9">
-        <v>7.0E-129</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C14" s="10">
+        <v>6.9999999999999995E-129</v>
+      </c>
+      <c r="D14" s="6">
         <v>0.4078</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="10" t="s">
+      <c r="F14" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G14" s="2"/>
+    </row>
+    <row r="15" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A15" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="9">
-        <v>4.0E-133</v>
-      </c>
-      <c r="D15" s="5">
-        <v>0.4136</v>
-      </c>
-      <c r="E15" s="4" t="s">
+      <c r="C15" s="10">
+        <v>4.0000000000000003E-133</v>
+      </c>
+      <c r="D15" s="6">
+        <v>0.41360000000000002</v>
+      </c>
+      <c r="E15" s="5" t="s">
         <v>8</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="10" t="s">
+      <c r="G15" s="2"/>
+    </row>
+    <row r="16" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A16" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C16" s="9">
-        <v>2.0E-171</v>
-      </c>
-      <c r="D16" s="5">
-        <v>0.5166</v>
-      </c>
-      <c r="E16" s="4" t="s">
+      <c r="C16" s="10">
+        <v>2E-171</v>
+      </c>
+      <c r="D16" s="6">
+        <v>0.51659999999999995</v>
+      </c>
+      <c r="E16" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F16" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="10" t="s">
+      <c r="F16" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G16" s="2"/>
+    </row>
+    <row r="17" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A17" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="C17" s="11">
-        <v>0.0</v>
-      </c>
-      <c r="D17" s="5">
-        <v>0.6374</v>
-      </c>
-      <c r="E17" s="4" t="s">
+      <c r="C17" s="12">
+        <v>0</v>
+      </c>
+      <c r="D17" s="6">
+        <v>0.63739999999999997</v>
+      </c>
+      <c r="E17" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F17" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="10" t="s">
+      <c r="F17" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G17" s="2"/>
+    </row>
+    <row r="18" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A18" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="9" t="s">
         <v>44</v>
       </c>
       <c r="C18" s="12">
-        <v>0.0</v>
-      </c>
-      <c r="D18" s="13">
-        <v>0.6394</v>
-      </c>
-      <c r="E18" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D18" s="6">
+        <v>0.63939999999999997</v>
+      </c>
+      <c r="E18" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F18" s="6" t="s">
+      <c r="F18" s="7" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="14"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
+      <c r="G18" s="2"/>
+    </row>
+    <row r="19" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A19" s="5"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="2"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="B2"/>
-    <hyperlink r:id="rId2" ref="B3"/>
-    <hyperlink r:id="rId3" ref="B4"/>
-    <hyperlink r:id="rId4" ref="B5"/>
-    <hyperlink r:id="rId5" ref="B6"/>
-    <hyperlink r:id="rId6" ref="B7"/>
-    <hyperlink r:id="rId7" ref="B8"/>
-    <hyperlink r:id="rId8" ref="B9"/>
-    <hyperlink r:id="rId9" ref="B10"/>
-    <hyperlink r:id="rId10" ref="B11"/>
-    <hyperlink r:id="rId11" ref="B12"/>
-    <hyperlink r:id="rId12" ref="B13"/>
-    <hyperlink r:id="rId13" ref="B14"/>
-    <hyperlink r:id="rId14" ref="B15"/>
-    <hyperlink r:id="rId15" ref="B16"/>
-    <hyperlink r:id="rId16" ref="B17"/>
-    <hyperlink r:id="rId17" ref="B18"/>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="B3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="B4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="B5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="B6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="B7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="B8" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="B9" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="B10" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="B11" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="B12" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="B13" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="B14" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="B15" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="B16" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="B17" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="B18" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
   </hyperlinks>
-  <drawing r:id="rId18"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>